--- a/ds/turmas/1DES_A/2º Semestre/01-bcd/aula02/pedidos/dados.xlsx
+++ b/ds/turmas/1DES_A/2º Semestre/01-bcd/aula02/pedidos/dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_A\2º Semestre\01-bcd\aula02\pedidos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C74B06B5-5595-493A-9A91-F493C21ED744}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58FEC545-603D-46E6-9905-85D90B72C4F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{D661FD12-BBDC-40B2-A3EA-689BFFFEA395}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{D661FD12-BBDC-40B2-A3EA-689BFFFEA395}"/>
   </bookViews>
   <sheets>
     <sheet name="produtos" sheetId="1" r:id="rId1"/>
@@ -424,9 +424,11 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -764,17 +766,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B6C98A3-D951-45B0-9DB7-2053F5057903}">
   <dimension ref="A1:F14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.21875" customWidth="1"/>
-    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.28515625" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -794,7 +796,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -811,7 +813,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -828,7 +830,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -845,7 +847,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -862,7 +864,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -879,7 +881,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -896,7 +898,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -913,7 +915,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -930,7 +932,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -947,7 +949,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -964,7 +966,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -981,7 +983,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -998,7 +1000,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1023,20 +1025,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FCD6C3A-DC26-4DA4-8E3A-2EAE2BB7EEB4}">
   <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.88671875" customWidth="1"/>
-    <col min="5" max="5" width="13.5546875" customWidth="1"/>
-    <col min="6" max="6" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" customWidth="1"/>
+    <col min="4" max="4" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C1" s="6" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1056,7 +1062,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1076,7 +1082,7 @@
         <v>46216</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1093,7 +1099,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1113,7 +1119,7 @@
         <v>46218</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1130,7 +1136,7 @@
         <v>46219</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1150,7 +1156,7 @@
         <v>46220</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1170,7 +1176,7 @@
         <v>46221</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1187,7 +1193,7 @@
         <v>46222</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1204,7 +1210,7 @@
         <v>46223</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1225,6 +1231,9 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C1:E1"/>
+  </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
@@ -1232,16 +1241,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{750EAA8D-E9F3-4E5A-8022-B7B81690BC2C}">
   <dimension ref="A1:F16"/>
-  <sheetFormatPr defaultColWidth="5.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="5.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" customWidth="1"/>
+    <col min="5" max="5" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1261,7 +1270,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1282,7 +1291,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1303,7 +1312,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1324,7 +1333,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1345,7 +1354,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1366,7 +1375,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1387,7 +1396,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1408,7 +1417,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1429,7 +1438,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1450,7 +1459,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1471,7 +1480,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1492,7 +1501,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1513,7 +1522,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1534,7 +1543,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1555,7 +1564,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1584,29 +1593,33 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C771A046-9131-4699-92B9-EEE2C0561A71}">
   <dimension ref="A1:E19"/>
-  <sheetFormatPr defaultColWidth="14.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="14.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="49.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="54.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>66</v>
       </c>
@@ -1623,7 +1636,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>66</v>
       </c>
@@ -1640,7 +1653,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>66</v>
       </c>
@@ -1657,7 +1670,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>66</v>
       </c>
@@ -1674,7 +1687,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>66</v>
       </c>
@@ -1691,7 +1704,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>66</v>
       </c>
@@ -1708,7 +1721,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>70</v>
       </c>
@@ -1725,7 +1738,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>70</v>
       </c>
@@ -1742,7 +1755,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>70</v>
       </c>
@@ -1759,7 +1772,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>70</v>
       </c>
@@ -1776,7 +1789,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>70</v>
       </c>
@@ -1793,7 +1806,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>70</v>
       </c>
@@ -1807,7 +1820,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>76</v>
       </c>
@@ -1824,7 +1837,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>76</v>
       </c>
@@ -1837,11 +1850,11 @@
       <c r="D15">
         <v>11</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>76</v>
       </c>
@@ -1854,11 +1867,11 @@
       <c r="D16">
         <v>11</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>76</v>
       </c>
@@ -1871,11 +1884,11 @@
       <c r="D17">
         <v>10.199999999999999</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>76</v>
       </c>
@@ -1888,11 +1901,11 @@
       <c r="D18">
         <v>11</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>76</v>
       </c>
@@ -1905,7 +1918,7 @@
       <c r="D19">
         <v>10.199999999999999</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" t="s">
         <v>97</v>
       </c>
     </row>
